--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_67_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_67_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -824,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -909,12 +909,12 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>14</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>7</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>5</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
         <v>2</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2511,16 +2511,16 @@
         <v>12</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X23" t="n">
         <v>6</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3099,7 +3099,7 @@
         <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3295,16 +3295,16 @@
         <v>10</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
@@ -3827,16 +3827,16 @@
         <v>113</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X30" t="n">
         <v>35</v>
@@ -4687,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>7</v>
@@ -4883,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>1</v>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X40" t="n">
         <v>6</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>1</v>
@@ -6062,10 +6062,10 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>1</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6787,13 +6787,13 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X48" t="n">
         <v>25</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_67_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_67_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="P2" t="n">
         <v>6</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>74.47</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>15</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>64.10</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1543,14 +1543,14 @@
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1739,10 +1739,10 @@
         <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2523,14 +2523,14 @@
         <v>3</v>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3307,14 +3307,14 @@
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>8</v>
       </c>
       <c r="X30" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="Y30" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4696,14 +4696,14 @@
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,14 +4892,14 @@
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5284,14 +5284,14 @@
         <v>3</v>
       </c>
       <c r="X40" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y40" t="n">
         <v>6</v>
       </c>
-      <c r="Y40" t="n">
-        <v>8</v>
-      </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6264,14 +6264,14 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6796,14 +6796,14 @@
         <v>7</v>
       </c>
       <c r="X48" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="Y48" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA48" t="n">
